--- a/samples/TRACE_입력양식_v0.5.xlsx
+++ b/samples/TRACE_입력양식_v0.5.xlsx
@@ -1915,7 +1915,7 @@
         <v>975365000</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>69329000</v>
+        <v>83885000</v>
       </c>
       <c r="G5" s="9" t="n">
         <v>232751000</v>
@@ -1942,7 +1942,7 @@
         <v>362274000</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>42182000</v>
+        <v>51038000</v>
       </c>
       <c r="G6" s="9" t="n">
         <v>142618000</v>
@@ -1969,7 +1969,7 @@
         <v>178565000</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>11161000</v>
+        <v>13505000</v>
       </c>
       <c r="G7" s="9" t="n">
         <v>38094000</v>

--- a/samples/TRACE_입력양식_v0.5.xlsx
+++ b/samples/TRACE_입력양식_v0.5.xlsx
@@ -15,6 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PL_원본" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예정사업비" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="부채변동표" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예산변경이력" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -102,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -120,6 +121,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -485,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C16"/>
+  <dimension ref="B2:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -624,6 +626,18 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>예산변경이력</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SAP 예산 변경이력 화면 · 추가배정·전용·집행시기변경 (예산월 → 옮긴월)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId1"/>
@@ -633,6 +647,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2248,4 +2263,240 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>TRACE · 예산변경이력 입력 양식</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>SAP 예산 변경이력 화면 · 추가배정·전용·집행시기변경 (예산월 → 옮긴월) · 예시 행은 가상 데이터</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="48" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>필수 · 대체 이름: 부서,팀코드,조직코드</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>선택 · 대체 이름: 팀명,조직명</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>필수 · 대체 이름: G/L계정,계정,계정코드</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>필수 · 대체 이름: 월,예산기간,기간 · 없을 때: 3 · 202603 · 2026-03 · 날짜 모두 가능</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>선택 · 대체 이름: 배정액,예산 · 없을 때: 참고용</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>선택 · 대체 이름: 이동월,변경월,옮긴기간 · 없을 때: 비면 추가배정·반납으로 봄</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>필수 · 대체 이름: 옮긴금액,이동금액,변경금액,금액</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>선택 · 대체 이름: 적요,사유,내용,비고 · 없을 때: '전용'·'반납' 구분 불가</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>부서코드</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>부서명</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>예산계정</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>예산월</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>예산금액</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>옮긴월</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>옮긴 금액</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>텍스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>D500</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>마케팅팀</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>62701000</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>150000000</v>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>90000000</v>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>가을 캠페인 일정 앞당김 (4분기 → 3분기)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>D800</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>고객서비스팀</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>62902000</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>콜센터 위탁 계약 갱신 지연</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>D400</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>상품개발팀</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>62901000</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>21000000</v>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>상품 자문 용역 종료월 변경</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>